--- a/CuraLive_Infrastructure_Costs.xlsx
+++ b/CuraLive_Infrastructure_Costs.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Service Overview" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Cost by Event Type" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Monthly Projections" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="OpenAI Token Details" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Optimization" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Annual Projection" state="visible" r:id="rId9"/>
+    <sheet sheetId="2" name="Platform Comparison" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Cost by Event Type" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Monthly Projections" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="OpenAI Token Details" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Optimization" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Annual Projection" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="226">
   <si>
     <t>Service / Application</t>
   </si>
@@ -33,7 +34,13 @@
     <t>Pricing Model</t>
   </si>
   <si>
-    <t>Fixed Monthly ($)</t>
+    <t>Current Monthly Cost ($)</t>
+  </si>
+  <si>
+    <t>Why $0 Now?</t>
+  </si>
+  <si>
+    <t>Fixed Monthly at Scale ($)</t>
   </si>
   <si>
     <t>Variable Per Event ($)</t>
@@ -48,12 +55,15 @@
     <t>Application hosting, deployment, SSL, auto-scaling compute</t>
   </si>
   <si>
-    <t>Pro / Teams</t>
+    <t>Replit Plan</t>
   </si>
   <si>
     <t>Fixed</t>
   </si>
   <si>
+    <t>Included in current Replit subscription</t>
+  </si>
+  <si>
     <t>MySQL Database</t>
   </si>
   <si>
@@ -63,31 +73,40 @@
     <t>Primary data store — sessions, archives, metrics, AI reports, CIP4 tables</t>
   </si>
   <si>
-    <t>Managed DB</t>
+    <t>Replit Managed</t>
   </si>
   <si>
     <t>Fixed + Storage</t>
   </si>
   <si>
+    <t>Included in Replit environment</t>
+  </si>
+  <si>
     <t>OpenAI GPT-4o</t>
   </si>
   <si>
     <t>AI / LLM</t>
   </si>
   <si>
-    <t>20-module AI report, crisis prediction, valuation impact, disclosure cert, compliance</t>
-  </si>
-  <si>
-    <t>API Pay-as-you-go</t>
+    <t>20-module AI report, crisis prediction, valuation impact, disclosure cert</t>
+  </si>
+  <si>
+    <t>Replit Integration</t>
   </si>
   <si>
     <t>Per Token</t>
   </si>
   <si>
+    <t>Bundled via Replit AI integration — not billed separately</t>
+  </si>
+  <si>
     <t>OpenAI GPT-4o-mini</t>
   </si>
   <si>
-    <t>Evolution engine, advisory bot, Bastion AI, support chat, quick analysis</t>
+    <t>Evolution engine, advisory bot, Bastion AI, support chat</t>
+  </si>
+  <si>
+    <t>Bundled via Replit AI integration</t>
   </si>
   <si>
     <t>OpenAI Whisper</t>
@@ -108,7 +127,13 @@
     <t>Meeting Bot</t>
   </si>
   <si>
-    <t>Bot joins Zoom/Teams/Meet for live Shadow Mode capture + real-time transcription</t>
+    <t>Bot joins Zoom/Teams/Meet for live Shadow Mode capture</t>
+  </si>
+  <si>
+    <t>API Key configured</t>
+  </si>
+  <si>
+    <t>No high-volume live sessions running yet</t>
   </si>
   <si>
     <t>Ably Realtime</t>
@@ -117,7 +142,7 @@
     <t>Messaging</t>
   </si>
   <si>
-    <t>Live transcript streaming to operators, OCC notifications, attendee updates</t>
+    <t>Live transcript streaming, OCC notifications</t>
   </si>
   <si>
     <t>Free Tier</t>
@@ -126,37 +151,43 @@
     <t>Per Message</t>
   </si>
   <si>
+    <t>Free tier: 6M messages/month</t>
+  </si>
+  <si>
     <t>Resend</t>
   </si>
   <si>
     <t>Email</t>
   </si>
   <si>
-    <t>Transactional emails — intelligence reports, reminders, registration confirmations</t>
-  </si>
-  <si>
-    <t>Free (100/day)</t>
+    <t>Transactional emails — intelligence reports, reminders</t>
   </si>
   <si>
     <t>Per Email</t>
   </si>
   <si>
+    <t>Free tier: 100 emails/day (3,000/month)</t>
+  </si>
+  <si>
     <t>Twilio</t>
   </si>
   <si>
     <t>Voice / Telco</t>
   </si>
   <si>
-    <t>Webphone, PSTN conference dial-out, voice bridging</t>
+    <t>Webphone, PSTN conference dial-out</t>
   </si>
   <si>
     <t>Pay-as-you-go</t>
   </si>
   <si>
+    <t>No voice calls being made yet</t>
+  </si>
+  <si>
     <t>Telnyx</t>
   </si>
   <si>
-    <t>Failover carrier for Africa/EMEA, WebRTC/SIP credentials</t>
+    <t>Failover carrier for Africa/EMEA</t>
   </si>
   <si>
     <t>Mux</t>
@@ -165,19 +196,22 @@
     <t>Video Streaming</t>
   </si>
   <si>
-    <t>RTMP live streaming ingest, HLS adaptive playback, recording storage</t>
+    <t>RTMP live streaming, HLS playback</t>
   </si>
   <si>
     <t>Per Minute + Views</t>
   </si>
   <si>
+    <t>No live webcasts running yet</t>
+  </si>
+  <si>
     <t>Stripe</t>
   </si>
   <si>
     <t>Payments</t>
   </si>
   <si>
-    <t>Subscription billing, customer management, payment processing</t>
+    <t>Subscription billing, payment processing</t>
   </si>
   <si>
     <t>Standard</t>
@@ -186,16 +220,49 @@
     <t>2.9% + $0.30/txn</t>
   </si>
   <si>
+    <t>No transactions processed yet</t>
+  </si>
+  <si>
     <t>GitHub</t>
   </si>
   <si>
     <t>Source Control</t>
   </si>
   <si>
-    <t>Repository hosting, version control, CI/CD integration</t>
-  </si>
-  <si>
-    <t>Free / Team</t>
+    <t>Repository hosting, version control</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>Free for public/private repos</t>
+  </si>
+  <si>
+    <t>Zoom</t>
+  </si>
+  <si>
+    <t>Meeting Platform</t>
+  </si>
+  <si>
+    <t>Target platform for Shadow Mode live capture</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>No cost</t>
+  </si>
+  <si>
+    <t>No integration needed — Recall.ai bot joins via meeting link</t>
+  </si>
+  <si>
+    <t>Microsoft Teams</t>
+  </si>
+  <si>
+    <t>Google Meet</t>
+  </si>
+  <si>
+    <t>Webex</t>
   </si>
   <si>
     <t>Shadow Guardian</t>
@@ -204,28 +271,97 @@
     <t>Internal Service</t>
   </si>
   <si>
-    <t>3-layer resilience — graceful shutdown, startup reconciliation, watchdog timer</t>
+    <t>3-layer resilience — shutdown, reconciliation, watchdog</t>
   </si>
   <si>
     <t>Built-in</t>
   </si>
   <si>
-    <t>No cost</t>
+    <t>Internal service — no external dependency</t>
   </si>
   <si>
     <t>System Diagnostics</t>
   </si>
   <si>
-    <t>15-check health monitoring — DB, AI, APIs, router registry</t>
+    <t>15-check health monitoring</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>TOTAL FIXED</t>
-  </si>
-  <si>
-    <t>TOTAL PER EVENT</t>
+    <t>TOTALS</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Integration Required?</t>
+  </si>
+  <si>
+    <t>API Subscription Needed?</t>
+  </si>
+  <si>
+    <t>App Marketplace Listing?</t>
+  </si>
+  <si>
+    <t>Platform Fee to CuraLive?</t>
+  </si>
+  <si>
+    <t>How CuraLive Connects</t>
+  </si>
+  <si>
+    <t>Bot Cost / 30-min Event ($)</t>
+  </si>
+  <si>
+    <t>Bot Cost / 60-min Event ($)</t>
+  </si>
+  <si>
+    <t>Bot Cost / 120-min Event ($)</t>
+  </si>
+  <si>
+    <t>AI Processing Cost ($)</t>
+  </si>
+  <si>
+    <t>Total Cost / 60-min Event ($)</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>$0</t>
+  </si>
+  <si>
+    <t>Recall.ai bot joins via meeting URL as a regular participant. No Zoom API or app approval needed.</t>
+  </si>
+  <si>
+    <t>Recall.ai bot joins via Teams meeting link. No Azure AD registration or Teams Admin approval needed.</t>
+  </si>
+  <si>
+    <t>Recall.ai bot joins via Meet link. No Google Workspace API setup needed.</t>
+  </si>
+  <si>
+    <t>Recall.ai bot joins via Webex meeting link. No Cisco integration required.</t>
+  </si>
+  <si>
+    <t>KEY TAKEAWAY</t>
+  </si>
+  <si>
+    <t>CuraLive does NOT integrate directly with any meeting platform. Recall.ai acts as a universal middle layer.</t>
+  </si>
+  <si>
+    <t>The Recall.ai bot joins meetings as a regular participant — just like any human attendee.</t>
+  </si>
+  <si>
+    <t>No API keys, marketplace listings, app approvals, or subscriptions needed from Zoom, Teams, Meet, or Webex.</t>
+  </si>
+  <si>
+    <t>If Recall.ai adds support for a new platform, CuraLive automatically supports it with zero development work.</t>
+  </si>
+  <si>
+    <t>The cost is identical across all platforms: $0.10/minute of bot time (Recall.ai) + AI processing (OpenAI).</t>
+  </si>
+  <si>
+    <t>Meeting hosts don't need to do anything special — the bot joins via the standard meeting link.</t>
   </si>
   <si>
     <t>Event Type</t>
@@ -234,91 +370,109 @@
     <t>Services Used</t>
   </si>
   <si>
+    <t>Platform Integration Cost ($)</t>
+  </si>
+  <si>
+    <t>Recall.ai Bot ($)</t>
+  </si>
+  <si>
+    <t>OpenAI GPT-4o ($)</t>
+  </si>
+  <si>
+    <t>OpenAI Mini ($)</t>
+  </si>
+  <si>
+    <t>Whisper ($)</t>
+  </si>
+  <si>
+    <t>Mux ($)</t>
+  </si>
+  <si>
+    <t>Total Per Event ($)</t>
+  </si>
+  <si>
+    <t>Live Shadow Mode — Zoom</t>
+  </si>
+  <si>
+    <t>Recall bot + 20-module AI report + Crisis + Valuation + Disclosure</t>
+  </si>
+  <si>
+    <t>Live Shadow Mode — Teams</t>
+  </si>
+  <si>
+    <t>Live Shadow Mode — Google Meet</t>
+  </si>
+  <si>
+    <t>Live Shadow Mode — Webex</t>
+  </si>
+  <si>
+    <t>Archive Upload (Audio/Video)</t>
+  </si>
+  <si>
+    <t>Any / Offline</t>
+  </si>
+  <si>
+    <t>Whisper transcription + full AI report pipeline</t>
+  </si>
+  <si>
+    <t>Transcript Paste (Text Only)</t>
+  </si>
+  <si>
+    <t>AI report pipeline only (no transcription needed)</t>
+  </si>
+  <si>
+    <t>Advisory Bot Query</t>
+  </si>
+  <si>
+    <t>Single GPT-4o call with context retrieval</t>
+  </si>
+  <si>
+    <t>Monthly Intelligence Report</t>
+  </si>
+  <si>
+    <t>Data aggregation + GPT-4o analysis + email</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Live Events</t>
+  </si>
+  <si>
+    <t>Archive Uploads</t>
+  </si>
+  <si>
+    <t>Transcript Pastes</t>
+  </si>
+  <si>
+    <t>Advisory Queries</t>
+  </si>
+  <si>
+    <t>Monthly Reports</t>
+  </si>
+  <si>
+    <t>Platform Fees ($)</t>
+  </si>
+  <si>
+    <t>Fixed Costs ($)</t>
+  </si>
+  <si>
     <t>Recall.ai ($)</t>
   </si>
   <si>
-    <t>OpenAI GPT-4o ($)</t>
-  </si>
-  <si>
-    <t>OpenAI Mini ($)</t>
-  </si>
-  <si>
-    <t>Whisper ($)</t>
-  </si>
-  <si>
-    <t>Mux ($)</t>
+    <t>OpenAI ($)</t>
   </si>
   <si>
     <t>Twilio ($)</t>
   </si>
   <si>
-    <t>Total Per Event ($)</t>
-  </si>
-  <si>
-    <t>Live Shadow Mode (Zoom/Teams/Meet)</t>
-  </si>
-  <si>
-    <t>Recall bot + Whisper + 20-module AI report + Crisis + Valuation + Disclosure + Ably streaming</t>
-  </si>
-  <si>
-    <t>Archive Upload (Audio/Video)</t>
-  </si>
-  <si>
-    <t>Whisper transcription + 20-module AI report + Crisis + Valuation + Disclosure</t>
-  </si>
-  <si>
-    <t>Transcript Paste (Text Only)</t>
-  </si>
-  <si>
-    <t>20-module AI report + Crisis + Valuation + Disclosure (no transcription)</t>
-  </si>
-  <si>
-    <t>Advisory Bot Query</t>
-  </si>
-  <si>
-    <t>Single GPT-4o call with event context retrieval</t>
-  </si>
-  <si>
-    <t>Monthly Intelligence Report</t>
-  </si>
-  <si>
-    <t>Aggregation of month's data + GPT-4o analysis + email delivery</t>
-  </si>
-  <si>
-    <t>Evolution Audit Run</t>
-  </si>
-  <si>
-    <t>GPT-4o-mini self-assessment + prompt optimization</t>
-  </si>
-  <si>
-    <t>Scenario</t>
-  </si>
-  <si>
-    <t>Live Events</t>
-  </si>
-  <si>
-    <t>Archive Uploads</t>
-  </si>
-  <si>
-    <t>Transcript Pastes</t>
-  </si>
-  <si>
-    <t>Advisory Queries</t>
-  </si>
-  <si>
-    <t>Monthly Reports</t>
-  </si>
-  <si>
-    <t>Fixed Costs ($)</t>
-  </si>
-  <si>
-    <t>OpenAI ($)</t>
-  </si>
-  <si>
     <t>TOTAL Monthly ($)</t>
   </si>
   <si>
-    <t>Current / Startup</t>
+    <t>Current (Today)</t>
+  </si>
+  <si>
+    <t>Startup</t>
   </si>
   <si>
     <t>Growth</t>
@@ -408,7 +562,7 @@
     <t>25 calls/event at $2.50/event</t>
   </si>
   <si>
-    <t>Move 10 lower-priority modules (social media, press release, etc.) to GPT-4o-mini</t>
+    <t>Move 10 lower-priority modules (social media, press release) to GPT-4o-mini</t>
   </si>
   <si>
     <t>~40% on AI costs</t>
@@ -423,7 +577,7 @@
     <t>Regenerating reports on repeat queries</t>
   </si>
   <si>
-    <t>Cache AI reports after first generation; serve cached version for subsequent views</t>
+    <t>Cache AI reports after first generation; serve cached for subsequent views</t>
   </si>
   <si>
     <t>~$0.50/repeat query</t>
@@ -435,7 +589,7 @@
     <t>$0.006/min — 30min avg per archive</t>
   </si>
   <si>
-    <t>Skip re-transcription of already-processed segments; use cheaper models for draft</t>
+    <t>Skip re-transcription of already-processed segments</t>
   </si>
   <si>
     <t>20-30% on whisper</t>
@@ -447,7 +601,7 @@
     <t>$1.50/event for encode + delivery</t>
   </si>
   <si>
-    <t>Use Mux only for public webcasts; skip for internal-only Shadow Mode sessions</t>
+    <t>Use Mux only for public webcasts; skip for Shadow Mode-only sessions</t>
   </si>
   <si>
     <t>Up to 100% for non-webcast</t>
@@ -459,7 +613,7 @@
     <t>Currently free tier (6M msg/mo)</t>
   </si>
   <si>
-    <t>Monitor usage — at scale, switch to self-hosted WebSocket if Ably costs increase</t>
+    <t>Monitor usage — at scale, consider self-hosted WebSocket</t>
   </si>
   <si>
     <t>Prevent future $29+/mo</t>
@@ -471,22 +625,28 @@
     <t>Advisory Bot Queries</t>
   </si>
   <si>
-    <t>$0.03/query — can scale with users</t>
-  </si>
-  <si>
-    <t>Use GPT-4o-mini for initial response; escalate to GPT-4o only for complex queries</t>
+    <t>$0.03/query — scales with users</t>
+  </si>
+  <si>
+    <t>Use GPT-4o-mini for initial response; GPT-4o only for complex queries</t>
   </si>
   <si>
     <t>~80% per query</t>
   </si>
   <si>
-    <t>Currently negligible cost</t>
-  </si>
-  <si>
-    <t>Pre-aggregate metrics daily; reduce token window for monthly synthesis</t>
-  </si>
-  <si>
-    <t>Minimal — already low</t>
+    <t>Platform Integration</t>
+  </si>
+  <si>
+    <t>$0 — no direct platform costs</t>
+  </si>
+  <si>
+    <t>Maintain Recall.ai abstraction layer; avoid building native Zoom/Teams apps</t>
+  </si>
+  <si>
+    <t>Avoids $10K+/yr dev cost</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
   <si>
     <t>Month</t>
@@ -544,7 +704,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -559,6 +719,25 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF34d399"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF34d399"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFfbbf24"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="FF94a3b8"/>
+      <sz val="11"/>
     </font>
     <font>
       <b/>
@@ -613,23 +792,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -972,7 +1159,7 @@
   <sheetPr>
     <tabColor rgb="FF60a5fa"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -980,11 +1167,13 @@
     <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="40" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1006,396 +1195,591 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4">
         <v>25</v>
       </c>
-      <c r="G2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="4">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="3">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>0</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
         <v>2.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F5" s="3">
         <v>0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <v>0.05</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
         <v>0.18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="4">
         <v>1</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="4">
         <v>0.21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
         <v>0.15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
         <v>1.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
       </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="F16" s="3">
         <v>0</v>
       </c>
-      <c r="G16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F17" s="6">
-        <f>SUM(F2:F16)</f>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G18" s="6">
-        <f>SUM(G2:G16)</f>
+      <c r="G16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="4">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H21" s="7">
+        <f>SUM(H2:H20)</f>
+      </c>
+      <c r="I21" s="7">
+        <f>SUM(I2:I20)</f>
       </c>
     </row>
   </sheetData>
@@ -1407,225 +1791,309 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF34d399"/>
+    <tabColor rgb="FF818cf8"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="7" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G2" s="4">
+        <v>3</v>
+      </c>
+      <c r="H2" s="4">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4">
+        <v>12</v>
+      </c>
+      <c r="J2" s="4">
+        <v>2.55</v>
+      </c>
+      <c r="K2" s="4">
+        <v>8.55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="4">
+        <v>3</v>
+      </c>
+      <c r="H3" s="4">
+        <v>6</v>
+      </c>
+      <c r="I3" s="4">
+        <v>12</v>
+      </c>
+      <c r="J3" s="4">
+        <v>2.55</v>
+      </c>
+      <c r="K3" s="4">
+        <v>8.55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="3">
+      <c r="B4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="4">
+        <v>3</v>
+      </c>
+      <c r="H4" s="4">
         <v>6</v>
       </c>
-      <c r="D2" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.21</v>
-      </c>
-      <c r="I2" s="3">
-        <v>10.26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="I4" s="4">
+        <v>12</v>
+      </c>
+      <c r="J4" s="4">
+        <v>2.55</v>
+      </c>
+      <c r="K4" s="4">
+        <v>8.55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.18</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
+      <c r="B5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="4">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4">
+        <v>6</v>
+      </c>
+      <c r="I5" s="4">
+        <v>12</v>
+      </c>
+      <c r="J5" s="4">
         <v>2.55</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0.02</v>
-      </c>
+      <c r="K5" s="4">
+        <v>8.55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A13:K13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -1634,245 +2102,308 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFfbbf24"/>
+    <tabColor rgb="FF34d399"/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="5" width="16" customWidth="1"/>
-    <col min="6" max="9" width="14" customWidth="1"/>
-    <col min="10" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="J2" s="4">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>6</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="J3" s="4">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="J4" s="4">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>6</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="J5" s="4">
+        <v>10.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.18</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.05</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="7">
-        <v>10</v>
-      </c>
-      <c r="C2" s="7">
-        <v>5</v>
-      </c>
-      <c r="D2" s="7">
-        <v>5</v>
-      </c>
-      <c r="E2" s="7">
-        <v>50</v>
-      </c>
-      <c r="F2" s="7">
-        <v>1</v>
-      </c>
-      <c r="G2" s="8">
-        <v>41</v>
-      </c>
-      <c r="H2" s="8">
-        <v>60</v>
-      </c>
-      <c r="I2" s="8">
-        <v>53.55</v>
-      </c>
-      <c r="J2" s="8">
-        <v>15</v>
-      </c>
-      <c r="K2" s="8">
-        <v>3.1</v>
-      </c>
-      <c r="L2" s="9">
-        <v>172.65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="7">
-        <v>25</v>
-      </c>
-      <c r="C3" s="7">
-        <v>15</v>
-      </c>
-      <c r="D3" s="7">
-        <v>10</v>
-      </c>
-      <c r="E3" s="7">
-        <v>200</v>
-      </c>
-      <c r="F3" s="7">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8">
-        <v>41</v>
-      </c>
-      <c r="H3" s="8">
-        <v>150</v>
-      </c>
-      <c r="I3" s="8">
-        <v>136.35</v>
-      </c>
-      <c r="J3" s="8">
-        <v>37.5</v>
-      </c>
-      <c r="K3" s="8">
-        <v>6.25</v>
-      </c>
-      <c r="L3" s="9">
-        <v>371.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="7">
-        <v>50</v>
-      </c>
-      <c r="C4" s="7">
-        <v>30</v>
-      </c>
-      <c r="D4" s="7">
-        <v>20</v>
-      </c>
-      <c r="E4" s="7">
-        <v>500</v>
-      </c>
-      <c r="F4" s="7">
-        <v>2</v>
-      </c>
-      <c r="G4" s="8">
-        <v>41</v>
-      </c>
-      <c r="H4" s="8">
-        <v>300</v>
-      </c>
-      <c r="I4" s="8">
-        <v>275.7</v>
-      </c>
-      <c r="J4" s="8">
-        <v>75</v>
-      </c>
-      <c r="K4" s="8">
-        <v>11.5</v>
-      </c>
-      <c r="L4" s="9">
-        <v>703.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="7">
-        <v>120</v>
-      </c>
-      <c r="C5" s="7">
-        <v>80</v>
-      </c>
-      <c r="D5" s="7">
-        <v>50</v>
-      </c>
-      <c r="E5" s="7">
-        <v>2000</v>
-      </c>
-      <c r="F5" s="7">
-        <v>4</v>
-      </c>
-      <c r="G5" s="8">
-        <v>41</v>
-      </c>
-      <c r="H5" s="8">
-        <v>720</v>
-      </c>
-      <c r="I5" s="8">
-        <v>712.5</v>
-      </c>
-      <c r="J5" s="8">
-        <v>180</v>
-      </c>
-      <c r="K5" s="8">
-        <v>26.2</v>
-      </c>
-      <c r="L5" s="9">
-        <v>1679.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="7">
-        <v>250</v>
-      </c>
-      <c r="C6" s="7">
-        <v>150</v>
-      </c>
-      <c r="D6" s="7">
-        <v>100</v>
-      </c>
-      <c r="E6" s="7">
-        <v>5000</v>
-      </c>
-      <c r="F6" s="7">
-        <v>8</v>
-      </c>
-      <c r="G6" s="8">
-        <v>41</v>
-      </c>
-      <c r="H6" s="8">
-        <v>1500</v>
-      </c>
-      <c r="I6" s="8">
-        <v>1453.2</v>
-      </c>
-      <c r="J6" s="8">
-        <v>375</v>
-      </c>
-      <c r="K6" s="8">
-        <v>53.5</v>
-      </c>
-      <c r="L6" s="9">
-        <v>3422.7</v>
+      <c r="C8" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.15</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -1882,6 +2413,317 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFfbbf24"/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="10" width="14" customWidth="1"/>
+    <col min="11" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="2">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>41</v>
+      </c>
+      <c r="I3" s="4">
+        <v>60</v>
+      </c>
+      <c r="J3" s="4">
+        <v>53.55</v>
+      </c>
+      <c r="K3" s="4">
+        <v>15</v>
+      </c>
+      <c r="L3" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="M3" s="10">
+        <v>172.65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="2">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2">
+        <v>200</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>41</v>
+      </c>
+      <c r="I4" s="4">
+        <v>150</v>
+      </c>
+      <c r="J4" s="4">
+        <v>136.35</v>
+      </c>
+      <c r="K4" s="4">
+        <v>37.5</v>
+      </c>
+      <c r="L4" s="4">
+        <v>6.25</v>
+      </c>
+      <c r="M4" s="10">
+        <v>371.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B5" s="2">
+        <v>50</v>
+      </c>
+      <c r="C5" s="2">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2">
+        <v>500</v>
+      </c>
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>41</v>
+      </c>
+      <c r="I5" s="4">
+        <v>300</v>
+      </c>
+      <c r="J5" s="4">
+        <v>275.7</v>
+      </c>
+      <c r="K5" s="4">
+        <v>75</v>
+      </c>
+      <c r="L5" s="4">
+        <v>11.5</v>
+      </c>
+      <c r="M5" s="10">
+        <v>703.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="2">
+        <v>120</v>
+      </c>
+      <c r="C6" s="2">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2">
+        <v>50</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2000</v>
+      </c>
+      <c r="F6" s="2">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>41</v>
+      </c>
+      <c r="I6" s="4">
+        <v>720</v>
+      </c>
+      <c r="J6" s="4">
+        <v>712.5</v>
+      </c>
+      <c r="K6" s="4">
+        <v>180</v>
+      </c>
+      <c r="L6" s="4">
+        <v>26.2</v>
+      </c>
+      <c r="M6" s="10">
+        <v>1679.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="2">
+        <v>250</v>
+      </c>
+      <c r="C7" s="2">
+        <v>150</v>
+      </c>
+      <c r="D7" s="2">
+        <v>100</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>41</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1500</v>
+      </c>
+      <c r="J7" s="4">
+        <v>1453.2</v>
+      </c>
+      <c r="K7" s="4">
+        <v>375</v>
+      </c>
+      <c r="L7" s="4">
+        <v>53.5</v>
+      </c>
+      <c r="M7" s="10">
+        <v>3422.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFa78bfa"/>
@@ -1898,146 +2740,146 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="A2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="4">
         <v>2.5</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="4">
         <v>10</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="2">
         <v>4000</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="2">
         <v>1500</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="2">
         <v>25</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="4">
         <v>2.5</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2" s="4">
         <v>125</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="4">
         <v>625</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B3" s="8">
+      <c r="A3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="4">
         <v>0.15</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="4">
         <v>0.6</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="2">
         <v>2000</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="2">
         <v>800</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="2">
         <v>15</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="4">
         <v>0.05</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="4">
         <v>2.5</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="4">
         <v>12.5</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="A4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="4">
         <v>0.18</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="4">
         <v>9</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="4">
         <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="8">
+      <c r="A5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.15</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="4">
         <v>0.6</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="2">
         <v>3000</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="2">
         <v>1000</v>
       </c>
-      <c r="F5" s="7">
-        <v>0</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8">
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2047,7 +2889,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFf87171"/>
@@ -2064,155 +2906,155 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>122</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>124</v>
+        <v>175</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>130</v>
+        <v>181</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>133</v>
+        <v>184</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>137</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>140</v>
+        <v>191</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>149</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>153</v>
+        <v>204</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>132</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>96</v>
+        <v>205</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>156</v>
+        <v>208</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>132</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -2221,295 +3063,337 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10b981"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
-    <col min="3" max="6" width="16" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="2">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>172.5</v>
+      </c>
+      <c r="G2" s="4">
+        <v>172.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="2">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2">
+        <v>57</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>198.51000000000002</v>
+      </c>
+      <c r="G3" s="4">
+        <v>371.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" s="2">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2">
+        <v>65</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>214.29</v>
+      </c>
+      <c r="G4" s="4">
+        <v>585.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B5" s="2">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2">
+        <v>73</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>235.04999999999998</v>
+      </c>
+      <c r="G5" s="4">
+        <v>820.3499999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B6" s="2">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2">
+        <v>80</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>250.8</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1071.1499999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B7" s="2">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2">
+        <v>88</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>276.84</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1347.9899999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="2">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2">
+        <v>10</v>
+      </c>
+      <c r="D8" s="2">
         <v>95</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>292.59</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1640.5799999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="2">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2">
         <v>10</v>
       </c>
-      <c r="C2" s="7">
-        <v>5</v>
-      </c>
-      <c r="D2" s="7">
-        <v>50</v>
-      </c>
-      <c r="E2" s="8">
-        <v>172.5</v>
-      </c>
-      <c r="F2" s="8">
-        <v>172.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="D9" s="2">
+        <v>102</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>313.32</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1953.8999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B10" s="2">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2">
+        <v>11</v>
+      </c>
+      <c r="D10" s="2">
+        <v>110</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
+        <v>329.1</v>
+      </c>
+      <c r="G10" s="4">
+        <v>2282.9999999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="2">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2">
         <v>12</v>
       </c>
-      <c r="C3" s="7">
-        <v>6</v>
-      </c>
-      <c r="D3" s="7">
-        <v>57</v>
-      </c>
-      <c r="E3" s="8">
-        <v>198.51000000000002</v>
-      </c>
-      <c r="F3" s="8">
-        <v>371.01</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="D11" s="2">
+        <v>117</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>344.84999999999997</v>
+      </c>
+      <c r="G11" s="4">
+        <v>2627.8499999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B12" s="2">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2">
         <v>13</v>
       </c>
-      <c r="C4" s="7">
-        <v>7</v>
-      </c>
-      <c r="D4" s="7">
-        <v>65</v>
-      </c>
-      <c r="E4" s="8">
-        <v>214.29</v>
-      </c>
-      <c r="F4" s="8">
-        <v>585.3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="B5" s="7">
-        <v>15</v>
-      </c>
-      <c r="C5" s="7">
-        <v>7</v>
-      </c>
-      <c r="D5" s="7">
-        <v>73</v>
-      </c>
-      <c r="E5" s="8">
-        <v>235.04999999999998</v>
-      </c>
-      <c r="F5" s="8">
-        <v>820.3499999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="7">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7">
-        <v>8</v>
-      </c>
-      <c r="D6" s="7">
-        <v>80</v>
-      </c>
-      <c r="E6" s="8">
-        <v>250.8</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1071.1499999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="7">
-        <v>18</v>
-      </c>
-      <c r="C7" s="7">
-        <v>9</v>
-      </c>
-      <c r="D7" s="7">
-        <v>88</v>
-      </c>
-      <c r="E7" s="8">
-        <v>276.84</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1347.9899999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="B8" s="7">
-        <v>19</v>
-      </c>
-      <c r="C8" s="7">
-        <v>10</v>
-      </c>
-      <c r="D8" s="7">
-        <v>95</v>
-      </c>
-      <c r="E8" s="8">
-        <v>292.59</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1640.5799999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="B9" s="7">
-        <v>21</v>
-      </c>
-      <c r="C9" s="7">
-        <v>10</v>
-      </c>
-      <c r="D9" s="7">
-        <v>102</v>
-      </c>
-      <c r="E9" s="8">
-        <v>313.32</v>
-      </c>
-      <c r="F9" s="8">
-        <v>1953.8999999999996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B10" s="7">
-        <v>22</v>
-      </c>
-      <c r="C10" s="7">
-        <v>11</v>
-      </c>
-      <c r="D10" s="7">
-        <v>110</v>
-      </c>
-      <c r="E10" s="8">
-        <v>329.1</v>
-      </c>
-      <c r="F10" s="8">
-        <v>2282.9999999999995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B11" s="7">
-        <v>23</v>
-      </c>
-      <c r="C11" s="7">
-        <v>12</v>
-      </c>
-      <c r="D11" s="7">
-        <v>117</v>
-      </c>
-      <c r="E11" s="8">
-        <v>344.84999999999997</v>
-      </c>
-      <c r="F11" s="8">
-        <v>2627.8499999999995</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="B12" s="7">
-        <v>25</v>
-      </c>
-      <c r="C12" s="7">
+      <c r="D12" s="2">
+        <v>125</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>370.89</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2998.7399999999993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" s="2">
+        <v>27</v>
+      </c>
+      <c r="C13" s="2">
         <v>13</v>
       </c>
-      <c r="D12" s="7">
-        <v>125</v>
-      </c>
-      <c r="E12" s="8">
-        <v>370.89</v>
-      </c>
-      <c r="F12" s="8">
-        <v>2998.7399999999993</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B13" s="7">
-        <v>27</v>
-      </c>
-      <c r="C13" s="7">
-        <v>13</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="D13" s="2">
         <v>133</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
         <v>391.65000000000003</v>
       </c>
-      <c r="F13" s="8">
+      <c r="G13" s="4">
         <v>3390.3899999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="11">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="10">
         <v>3390.3899999999994</v>
       </c>
     </row>
